--- a/Result/profitability/2719.xlsx
+++ b/Result/profitability/2719.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM69"/>
+  <dimension ref="A1:AM70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-1.67</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.205</v>
+        <v>-0.2375</v>
       </c>
       <c r="N2" t="n">
-        <v>6.743749999999999</v>
+        <v>7.6125</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-4.43</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.76625</v>
+        <v>-0.7112499999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>7.48125</v>
+        <v>9.19875</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-1.06</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.8187500000000001</v>
+        <v>-0.86375</v>
       </c>
       <c r="N4" t="n">
-        <v>9.58625</v>
+        <v>10.12625</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.66</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.9212499999999999</v>
+        <v>-0.8912499999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>10.2875</v>
+        <v>11.24125</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>1.2</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.7162500000000001</v>
+        <v>-0.7175</v>
       </c>
       <c r="N6" t="n">
-        <v>11.50625</v>
+        <v>12.61</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,16 +1264,16 @@
         <v>0.82</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.59</v>
+        <v>-0.65625</v>
       </c>
       <c r="N7" t="n">
-        <v>12.62375</v>
+        <v>13.1075</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
       </c>
       <c r="P7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1282,7 +1282,7 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.74</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.53875</v>
+        <v>-0.6575</v>
       </c>
       <c r="N8" t="n">
-        <v>13.32375</v>
+        <v>12.645</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9191,6 +9191,133 @@
       </c>
       <c r="AM69" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2719</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>327</v>
+      </c>
+      <c r="D70" t="n">
+        <v>290</v>
+      </c>
+      <c r="E70" t="n">
+        <v>37</v>
+      </c>
+      <c r="F70" t="n">
+        <v>11.28</v>
+      </c>
+      <c r="G70" t="n">
+        <v>5</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>1.39%</t>
+        </is>
+      </c>
+      <c r="I70" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J70" t="n">
+        <v>-12</v>
+      </c>
+      <c r="K70" t="n">
+        <v>-14</v>
+      </c>
+      <c r="L70" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="M70" t="n">
+        <v>-0.02125000000000001</v>
+      </c>
+      <c r="N70" t="n">
+        <v>6.29125</v>
+      </c>
+      <c r="O70" t="n">
+        <v>0</v>
+      </c>
+      <c r="P70" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>0</v>
+      </c>
+      <c r="R70" t="n">
+        <v>0</v>
+      </c>
+      <c r="S70" t="n">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>0</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
+      </c>
+      <c r="V70" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W70" t="n">
+        <v>-0.95</v>
+      </c>
+      <c r="X70" t="n">
+        <v>-1.266666666666667</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>-5.430000000000001</v>
+      </c>
+      <c r="Z70" t="n">
+        <v>-0.3249551166965889</v>
+      </c>
+      <c r="AA70" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AB70" t="n">
+        <v>-0.5454545454545454</v>
+      </c>
+      <c r="AC70" t="n">
+        <v>7.629999999999999</v>
+      </c>
+      <c r="AD70" t="n">
+        <v>2.090410958904109</v>
+      </c>
+      <c r="AE70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK70" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL70" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM70" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
